--- a/data/stx_xlsx/WALLb.ST.xlsx
+++ b/data/stx_xlsx/WALLb.ST.xlsx
@@ -12236,15 +12236,34 @@
       <c r="N54" s="16">
         <v>26463.19</v>
       </c>
-      <c r="O54" s="16"/>
-      <c r="P54" s="16"/>
-      <c r="Q54" s="16"/>
-      <c r="R54" s="16"/>
-      <c r="S54" s="16"/>
-      <c r="T54" s="16"/>
-      <c r="U54" s="16"/>
-      <c r="V54" s="16"/>
-      <c r="W54" s="16"/>
+      <c r="O54" s="16">
+        <v>23694.93</v>
+      </c>
+      <c r="P54" s="16">
+        <v>22817.25</v>
+      </c>
+      <c r="Q54" s="16">
+        <v>20508.79</v>
+      </c>
+      <c r="R54" s="16">
+        <v>16771.26</v>
+      </c>
+      <c r="S54" s="16">
+        <v>16041.64</v>
+      </c>
+      <c r="T54" s="16">
+        <v>15072.37</v>
+      </c>
+      <c r="U54" s="16">
+        <v>16643.44</v>
+      </c>
+      <c r="V54" s="16">
+        <v>13673.14</v>
+      </c>
+      <c r="W54" s="15">
+        <f>SUM(W65,W44)</f>
+        <v>12437.53</v>
+      </c>
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
